--- a/Peiling.xlsx
+++ b/Peiling.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\G.deLange\Documents\GitHub\peilingen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06C6620B-4928-4ACA-BACC-74C0DE978AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD9F52C1-6833-4864-B03C-3C8F4AFA20DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{F860C830-3069-4E45-9470-11FABD2A9123}"/>
   </bookViews>
